--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,28 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>EDNA</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
   </si>
 </sst>
 </file>
@@ -504,19 +489,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>73.53</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -530,19 +515,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -556,19 +541,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>80.56</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -582,19 +567,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>90.7</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -608,19 +593,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>83.72</v>
+        <v>97.67</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -634,10 +619,10 @@
         <v>24</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
       </c>
       <c r="F7">
         <v>23</v>
@@ -699,16 +684,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.34999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -722,16 +710,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -745,16 +736,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
         <v>29</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>80.56</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -768,16 +762,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -791,16 +788,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
         <v>36</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>83.72</v>
+      </c>
+      <c r="H6">
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -814,16 +814,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -876,19 +879,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>73.53</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,19 +905,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -928,19 +931,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>80.56</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -954,19 +957,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>74.42</v>
+        <v>90.7</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -980,16 +983,16 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>83.72</v>
+        <v>97.67</v>
       </c>
       <c r="H6">
         <v>7.3</v>
@@ -1006,10 +1009,10 @@
         <v>24</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
       </c>
       <c r="F7">
         <v>23</v>
@@ -1018,7 +1021,7 @@
         <v>95.83</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1060,71 +1063,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920168</v>
+        <v>21330051920197</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920241</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920297</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
@@ -684,19 +684,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,19 +710,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>64.52</v>
+        <v>70.97</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,19 +736,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>80.56</v>
+        <v>86.11</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -762,19 +762,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>81.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -788,19 +788,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>83.72</v>
+        <v>93.02</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -814,19 +814,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -908,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -943,7 +943,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
   </si>
 </sst>
 </file>
@@ -684,19 +675,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +701,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -736,19 +727,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>86.11</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -788,16 +779,16 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>93.02</v>
+        <v>97.67</v>
       </c>
       <c r="H6">
         <v>7.1</v>
@@ -814,16 +805,16 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H7">
         <v>7.3</v>
@@ -882,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>77.42</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -934,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>90.7</v>
+        <v>93.02</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6">
-        <v>97.67</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1061,29 +1052,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920197</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
